--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129999020</v>
+        <v>129999022</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465247</v>
+        <v>465249</v>
       </c>
       <c r="R2" t="n">
-        <v>6988974</v>
+        <v>6988960</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129999022</v>
+        <v>129999020</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465249</v>
+        <v>465247</v>
       </c>
       <c r="R3" t="n">
-        <v>6988960</v>
+        <v>6988974</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -948,7 +948,7 @@
         <v>129999016</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129999025</v>
+        <v>129999029</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465248</v>
+        <v>465253</v>
       </c>
       <c r="R5" t="n">
-        <v>6988949</v>
+        <v>6988934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129999029</v>
+        <v>129999030</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>465253</v>
       </c>
       <c r="R6" t="n">
-        <v>6988934</v>
+        <v>6988930</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129999030</v>
+        <v>129999052</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,29 +1361,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1393,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465253</v>
+        <v>465316</v>
       </c>
       <c r="R7" t="n">
-        <v>6988930</v>
+        <v>6988887</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,7 +1428,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en hyggeskant.</t>
+          <t>Växer resupinat i en grov granlåga av knäckt gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,6 +1437,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1462,12 +1458,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1485,10 +1481,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999052</v>
+        <v>129999024</v>
       </c>
       <c r="B8" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1496,24 +1492,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1523,10 +1524,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465316</v>
+        <v>465247</v>
       </c>
       <c r="R8" t="n">
-        <v>6988887</v>
+        <v>6988955</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1563,7 +1564,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Växer resupinat i en grov granlåga av knäckt gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1572,7 +1573,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999024</v>
+        <v>129999027</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465247</v>
+        <v>465253</v>
       </c>
       <c r="R9" t="n">
-        <v>6988955</v>
+        <v>6988941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1751,10 +1751,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999023</v>
+        <v>129999031</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1794,10 +1794,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465246</v>
+        <v>465257</v>
       </c>
       <c r="R10" t="n">
-        <v>6988958</v>
+        <v>6988924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1886,7 +1886,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999027</v>
+        <v>129999041</v>
       </c>
       <c r="B11" t="n">
         <v>57737</v>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1914,25 +1914,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465253</v>
+        <v>465327</v>
       </c>
       <c r="R11" t="n">
-        <v>6988941</v>
+        <v>6988874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1969,7 +1977,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1983,27 +1991,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2021,10 +2009,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999041</v>
+        <v>129999021</v>
       </c>
       <c r="B12" t="n">
-        <v>57734</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,16 +2020,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2049,33 +2037,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465327</v>
+        <v>465246</v>
       </c>
       <c r="R12" t="n">
-        <v>6988874</v>
+        <v>6988967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2112,7 +2092,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2106,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129999031</v>
+        <v>129999017</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2187,10 +2187,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465257</v>
+        <v>465239</v>
       </c>
       <c r="R13" t="n">
-        <v>6988924</v>
+        <v>6988991</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2279,10 +2279,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129999021</v>
+        <v>129999019</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465246</v>
+        <v>465242</v>
       </c>
       <c r="R14" t="n">
-        <v>6988967</v>
+        <v>6988979</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999017</v>
+        <v>129999050</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>91601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2425,29 +2425,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2457,10 +2456,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465239</v>
+        <v>465391</v>
       </c>
       <c r="R15" t="n">
-        <v>6988991</v>
+        <v>6988830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2497,7 +2496,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2506,6 +2505,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129999019</v>
+        <v>129999015</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465242</v>
+        <v>465240</v>
       </c>
       <c r="R16" t="n">
-        <v>6988979</v>
+        <v>6989018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2684,10 +2684,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129999050</v>
+        <v>129999028</v>
       </c>
       <c r="B17" t="n">
-        <v>91598</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2695,28 +2695,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2726,10 +2727,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465391</v>
+        <v>465250</v>
       </c>
       <c r="R17" t="n">
-        <v>6988830</v>
+        <v>6988939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2766,7 +2767,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2775,7 +2776,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2796,12 +2796,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129999015</v>
+        <v>129999026</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465240</v>
+        <v>465249</v>
       </c>
       <c r="R18" t="n">
-        <v>6989018</v>
+        <v>6988942</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129999028</v>
+        <v>129999053</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2965,29 +2965,24 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2997,10 +2992,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465250</v>
+        <v>465330</v>
       </c>
       <c r="R19" t="n">
-        <v>6988939</v>
+        <v>6988815</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3037,7 +3032,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3046,6 +3041,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3064,14 +3060,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3089,10 +3080,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129999026</v>
+        <v>129999018</v>
       </c>
       <c r="B20" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3132,10 +3123,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465249</v>
+        <v>465241</v>
       </c>
       <c r="R20" t="n">
-        <v>6988942</v>
+        <v>6988985</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3224,10 +3215,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129999053</v>
+        <v>129999025</v>
       </c>
       <c r="B21" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3235,24 +3226,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3262,10 +3258,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>465330</v>
+        <v>465248</v>
       </c>
       <c r="R21" t="n">
-        <v>6988815</v>
+        <v>6988949</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3302,7 +3298,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,7 +3307,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3330,9 +3325,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129999018</v>
+        <v>129999023</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>465241</v>
+        <v>465246</v>
       </c>
       <c r="R22" t="n">
-        <v>6988985</v>
+        <v>6988958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -2414,10 +2414,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999050</v>
+        <v>129999015</v>
       </c>
       <c r="B15" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2425,28 +2425,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2456,10 +2457,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465391</v>
+        <v>465240</v>
       </c>
       <c r="R15" t="n">
-        <v>6988830</v>
+        <v>6989018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2496,7 +2497,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2505,7 +2506,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129999015</v>
+        <v>129999050</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>91601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,29 +2560,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2592,10 +2591,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465240</v>
+        <v>465391</v>
       </c>
       <c r="R16" t="n">
-        <v>6989018</v>
+        <v>6988830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2632,7 +2631,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2640,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129999022</v>
+        <v>129999020</v>
       </c>
       <c r="B2" t="n">
         <v>57740</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465249</v>
+        <v>465247</v>
       </c>
       <c r="R2" t="n">
-        <v>6988960</v>
+        <v>6988974</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,7 +810,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129999020</v>
+        <v>129999022</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -843,7 +843,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465247</v>
+        <v>465249</v>
       </c>
       <c r="R3" t="n">
-        <v>6988974</v>
+        <v>6988960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1616,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999027</v>
+        <v>129999041</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1644,25 +1644,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465253</v>
+        <v>465327</v>
       </c>
       <c r="R9" t="n">
-        <v>6988941</v>
+        <v>6988874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1707,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,27 +1721,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1751,7 +1739,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999031</v>
+        <v>129999027</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1794,10 +1782,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465257</v>
+        <v>465253</v>
       </c>
       <c r="R10" t="n">
-        <v>6988924</v>
+        <v>6988941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1886,10 +1874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999041</v>
+        <v>129999021</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,16 +1885,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1914,33 +1902,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465327</v>
+        <v>465246</v>
       </c>
       <c r="R11" t="n">
-        <v>6988874</v>
+        <v>6988967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1977,7 +1957,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1991,7 +1971,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999021</v>
+        <v>129999031</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465246</v>
+        <v>465257</v>
       </c>
       <c r="R12" t="n">
-        <v>6988967</v>
+        <v>6988924</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999015</v>
+        <v>129999050</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>91601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2425,29 +2425,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2457,10 +2456,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465240</v>
+        <v>465391</v>
       </c>
       <c r="R15" t="n">
-        <v>6989018</v>
+        <v>6988830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2497,7 +2496,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2506,6 +2505,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129999050</v>
+        <v>129999015</v>
       </c>
       <c r="B16" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,28 +2560,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2591,10 +2592,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465391</v>
+        <v>465240</v>
       </c>
       <c r="R16" t="n">
-        <v>6988830</v>
+        <v>6989018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2631,7 +2632,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2641,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1353,7 +1353,7 @@
         <v>129999052</v>
       </c>
       <c r="B7" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999021</v>
+        <v>129999031</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465246</v>
+        <v>465257</v>
       </c>
       <c r="R11" t="n">
-        <v>6988967</v>
+        <v>6988924</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999031</v>
+        <v>129999021</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465257</v>
+        <v>465246</v>
       </c>
       <c r="R12" t="n">
-        <v>6988924</v>
+        <v>6988967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999050</v>
+        <v>129999015</v>
       </c>
       <c r="B15" t="n">
-        <v>91601</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2425,28 +2425,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2456,10 +2457,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465391</v>
+        <v>465240</v>
       </c>
       <c r="R15" t="n">
-        <v>6988830</v>
+        <v>6989018</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2496,7 +2497,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2505,7 +2506,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2549,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129999015</v>
+        <v>129999050</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,29 +2560,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2592,10 +2591,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465240</v>
+        <v>465391</v>
       </c>
       <c r="R16" t="n">
-        <v>6989018</v>
+        <v>6988830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2632,7 +2631,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,6 +2640,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
         <v>129999053</v>
       </c>
       <c r="B19" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999027</v>
+        <v>129999021</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465253</v>
+        <v>465246</v>
       </c>
       <c r="R10" t="n">
-        <v>6988941</v>
+        <v>6988967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999031</v>
+        <v>129999027</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465257</v>
+        <v>465253</v>
       </c>
       <c r="R11" t="n">
-        <v>6988924</v>
+        <v>6988941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999021</v>
+        <v>129999031</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465246</v>
+        <v>465257</v>
       </c>
       <c r="R12" t="n">
-        <v>6988967</v>
+        <v>6988924</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129999019</v>
+        <v>129999050</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>91602</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,29 +2290,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2322,10 +2321,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465242</v>
+        <v>465391</v>
       </c>
       <c r="R14" t="n">
-        <v>6988979</v>
+        <v>6988830</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2362,7 +2361,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2371,6 +2370,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999015</v>
+        <v>129999019</v>
       </c>
       <c r="B15" t="n">
         <v>57740</v>
@@ -2447,7 +2447,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465240</v>
+        <v>465242</v>
       </c>
       <c r="R15" t="n">
-        <v>6989018</v>
+        <v>6988979</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2549,10 +2549,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129999050</v>
+        <v>129999015</v>
       </c>
       <c r="B16" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,28 +2560,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2591,10 +2592,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465391</v>
+        <v>465240</v>
       </c>
       <c r="R16" t="n">
-        <v>6988830</v>
+        <v>6989018</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2631,7 +2632,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2641,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1739,7 +1739,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999021</v>
+        <v>129999027</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465246</v>
+        <v>465253</v>
       </c>
       <c r="R10" t="n">
-        <v>6988967</v>
+        <v>6988941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999027</v>
+        <v>129999031</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465253</v>
+        <v>465257</v>
       </c>
       <c r="R11" t="n">
-        <v>6988941</v>
+        <v>6988924</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999031</v>
+        <v>129999021</v>
       </c>
       <c r="B12" t="n">
         <v>57740</v>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465257</v>
+        <v>465246</v>
       </c>
       <c r="R12" t="n">
-        <v>6988924</v>
+        <v>6988967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1353,7 +1353,7 @@
         <v>129999052</v>
       </c>
       <c r="B7" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999041</v>
+        <v>129999027</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1644,33 +1644,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465327</v>
+        <v>465253</v>
       </c>
       <c r="R9" t="n">
-        <v>6988874</v>
+        <v>6988941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1707,7 +1699,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1713,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1739,7 +1751,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999027</v>
+        <v>129999031</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1782,10 +1794,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465253</v>
+        <v>465257</v>
       </c>
       <c r="R10" t="n">
-        <v>6988941</v>
+        <v>6988924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1874,7 +1886,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999031</v>
+        <v>129999021</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1917,10 +1929,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465257</v>
+        <v>465246</v>
       </c>
       <c r="R11" t="n">
-        <v>6988924</v>
+        <v>6988967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2009,10 +2021,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999021</v>
+        <v>129999041</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2020,16 +2032,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2037,25 +2049,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465246</v>
+        <v>465327</v>
       </c>
       <c r="R12" t="n">
-        <v>6988967</v>
+        <v>6988874</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,7 +2112,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,27 +2126,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2282,7 +2282,7 @@
         <v>129999050</v>
       </c>
       <c r="B14" t="n">
-        <v>91602</v>
+        <v>91619</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>129999053</v>
       </c>
       <c r="B19" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999041</v>
+        <v>129999027</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1644,33 +1644,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465327</v>
+        <v>465253</v>
       </c>
       <c r="R9" t="n">
-        <v>6988874</v>
+        <v>6988941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1707,7 +1699,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1713,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1739,7 +1751,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999027</v>
+        <v>129999031</v>
       </c>
       <c r="B10" t="n">
         <v>57741</v>
@@ -1782,10 +1794,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465253</v>
+        <v>465257</v>
       </c>
       <c r="R10" t="n">
-        <v>6988941</v>
+        <v>6988924</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1874,7 +1886,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999031</v>
+        <v>129999021</v>
       </c>
       <c r="B11" t="n">
         <v>57741</v>
@@ -1917,10 +1929,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465257</v>
+        <v>465246</v>
       </c>
       <c r="R11" t="n">
-        <v>6988924</v>
+        <v>6988967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2009,10 +2021,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999021</v>
+        <v>129999041</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2020,16 +2032,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2037,25 +2049,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465246</v>
+        <v>465327</v>
       </c>
       <c r="R12" t="n">
-        <v>6988967</v>
+        <v>6988874</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,7 +2112,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2106,27 +2126,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999027</v>
+        <v>129999041</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1644,25 +1644,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465253</v>
+        <v>465327</v>
       </c>
       <c r="R9" t="n">
-        <v>6988941</v>
+        <v>6988874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1707,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,27 +1721,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1751,7 +1739,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999031</v>
+        <v>129999027</v>
       </c>
       <c r="B10" t="n">
         <v>57741</v>
@@ -1794,10 +1782,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465257</v>
+        <v>465253</v>
       </c>
       <c r="R10" t="n">
-        <v>6988924</v>
+        <v>6988941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1886,7 +1874,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999021</v>
+        <v>129999031</v>
       </c>
       <c r="B11" t="n">
         <v>57741</v>
@@ -1929,10 +1917,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465246</v>
+        <v>465257</v>
       </c>
       <c r="R11" t="n">
-        <v>6988967</v>
+        <v>6988924</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2021,10 +2009,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999041</v>
+        <v>129999021</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,16 +2020,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2049,33 +2037,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465327</v>
+        <v>465246</v>
       </c>
       <c r="R12" t="n">
-        <v>6988874</v>
+        <v>6988967</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2112,7 +2092,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2106,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -1353,7 +1353,7 @@
         <v>129999052</v>
       </c>
       <c r="B7" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -2279,10 +2279,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129999050</v>
+        <v>129999019</v>
       </c>
       <c r="B14" t="n">
-        <v>91635</v>
+        <v>57741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,28 +2290,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2321,10 +2322,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465391</v>
+        <v>465242</v>
       </c>
       <c r="R14" t="n">
-        <v>6988830</v>
+        <v>6988979</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,7 +2362,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,7 +2371,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2391,12 +2391,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999019</v>
+        <v>129999050</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>91637</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2425,29 +2425,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2457,10 +2456,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465242</v>
+        <v>465391</v>
       </c>
       <c r="R15" t="n">
-        <v>6988979</v>
+        <v>6988830</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2497,7 +2496,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2506,6 +2505,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2526,12 +2526,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2957,7 +2957,7 @@
         <v>129999053</v>
       </c>
       <c r="B19" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129999020</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>129999022</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         <v>129999016</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>129999029</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>129999030</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>129999052</v>
       </c>
       <c r="B7" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129999024</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999041</v>
+        <v>129999027</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1627,16 +1627,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1644,33 +1644,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465327</v>
+        <v>465253</v>
       </c>
       <c r="R9" t="n">
-        <v>6988874</v>
+        <v>6988941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1707,7 +1699,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1721,7 +1713,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1739,10 +1751,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999027</v>
+        <v>129999041</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,16 +1762,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1767,25 +1779,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465253</v>
+        <v>465327</v>
       </c>
       <c r="R10" t="n">
-        <v>6988941</v>
+        <v>6988874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1822,7 +1842,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1836,27 +1856,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1877,7 +1877,7 @@
         <v>129999031</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>129999021</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>129999017</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>129999019</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>129999050</v>
       </c>
       <c r="B15" t="n">
-        <v>91637</v>
+        <v>91724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>129999015</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>129999028</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>129999026</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>129999053</v>
       </c>
       <c r="B19" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
         <v>129999018</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>129999025</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>129999023</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129999020</v>
+        <v>129999050</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,29 +686,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465247</v>
+        <v>465391</v>
       </c>
       <c r="R2" t="n">
-        <v>6988974</v>
+        <v>6988830</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -810,27 +810,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129999022</v>
+        <v>129999041</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -838,25 +838,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465249</v>
+        <v>465327</v>
       </c>
       <c r="R3" t="n">
-        <v>6988960</v>
+        <v>6988874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +915,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -945,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129999016</v>
+        <v>129999015</v>
       </c>
       <c r="B4" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,10 +976,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465236</v>
+        <v>465240</v>
       </c>
       <c r="R4" t="n">
-        <v>6989008</v>
+        <v>6989018</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1016,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129999029</v>
+        <v>129999016</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1101,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1123,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>465253</v>
+        <v>465236</v>
       </c>
       <c r="R5" t="n">
-        <v>6988934</v>
+        <v>6989008</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1151,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1215,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129999030</v>
+        <v>129999017</v>
       </c>
       <c r="B6" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,10 +1246,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>465253</v>
+        <v>465239</v>
       </c>
       <c r="R6" t="n">
-        <v>6988930</v>
+        <v>6988991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1298,7 +1286,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en smal gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1350,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129999052</v>
+        <v>129999018</v>
       </c>
       <c r="B7" t="n">
-        <v>91748</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,24 +1349,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1388,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465316</v>
+        <v>465241</v>
       </c>
       <c r="R7" t="n">
-        <v>6988887</v>
+        <v>6988985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,7 +1421,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Växer resupinat i en grov granlåga av knäckt gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1437,7 +1430,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1458,12 +1450,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1481,10 +1473,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129999024</v>
+        <v>129999019</v>
       </c>
       <c r="B8" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1524,10 +1516,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>465247</v>
+        <v>465242</v>
       </c>
       <c r="R8" t="n">
-        <v>6988955</v>
+        <v>6988979</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1616,10 +1608,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129999027</v>
+        <v>129999020</v>
       </c>
       <c r="B9" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1649,7 +1641,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1659,10 +1651,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>465253</v>
+        <v>465247</v>
       </c>
       <c r="R9" t="n">
-        <v>6988941</v>
+        <v>6988974</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1699,7 +1691,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1751,10 +1743,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129999031</v>
+        <v>129999021</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1794,10 +1786,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>465257</v>
+        <v>465246</v>
       </c>
       <c r="R10" t="n">
-        <v>6988924</v>
+        <v>6988967</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1886,10 +1878,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129999021</v>
+        <v>129999022</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1929,10 +1921,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>465246</v>
+        <v>465249</v>
       </c>
       <c r="R11" t="n">
-        <v>6988967</v>
+        <v>6988960</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2021,10 +2013,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129999041</v>
+        <v>129999023</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,16 +2024,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2049,33 +2041,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sluten/Gåxmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465327</v>
+        <v>465246</v>
       </c>
       <c r="R12" t="n">
-        <v>6988874</v>
+        <v>6988958</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2112,7 +2096,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1 individ med tydligt lockläte i barrblandskog där det även finns troliga hackspår efter spillkråka.</t>
+          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,7 +2110,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2144,10 +2148,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129999017</v>
+        <v>129999024</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2187,10 +2191,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>465239</v>
+        <v>465247</v>
       </c>
       <c r="R13" t="n">
-        <v>6988991</v>
+        <v>6988955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2279,10 +2283,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129999050</v>
+        <v>129999025</v>
       </c>
       <c r="B14" t="n">
-        <v>91724</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,28 +2294,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2321,10 +2326,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>465391</v>
+        <v>465248</v>
       </c>
       <c r="R14" t="n">
-        <v>6988830</v>
+        <v>6988949</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,7 +2366,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd i granskog.</t>
+          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,7 +2375,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2391,12 +2395,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2414,10 +2418,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129999019</v>
+        <v>129999026</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2457,10 +2461,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>465242</v>
+        <v>465249</v>
       </c>
       <c r="R15" t="n">
-        <v>6988979</v>
+        <v>6988942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2549,10 +2553,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129999015</v>
+        <v>129999027</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2592,10 +2596,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>465240</v>
+        <v>465253</v>
       </c>
       <c r="R16" t="n">
-        <v>6989018</v>
+        <v>6988941</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2632,7 +2636,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, i riklig mängd på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2687,7 +2691,7 @@
         <v>129999028</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2819,10 +2823,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129999026</v>
+        <v>129999029</v>
       </c>
       <c r="B18" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2862,10 +2866,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>465249</v>
+        <v>465253</v>
       </c>
       <c r="R18" t="n">
-        <v>6988942</v>
+        <v>6988934</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2954,10 +2958,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129999053</v>
+        <v>129999030</v>
       </c>
       <c r="B19" t="n">
-        <v>91748</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2965,24 +2969,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2992,10 +3001,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465330</v>
+        <v>465253</v>
       </c>
       <c r="R19" t="n">
-        <v>6988815</v>
+        <v>6988930</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3032,7 +3041,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack (savhack), färska, på en smal gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3041,7 +3050,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3060,9 +3068,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,10 +3093,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129999018</v>
+        <v>129999031</v>
       </c>
       <c r="B20" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3113,7 +3126,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3123,10 +3136,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465241</v>
+        <v>465257</v>
       </c>
       <c r="R20" t="n">
-        <v>6988985</v>
+        <v>6988924</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3163,7 +3176,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid en hyggeskant.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid en hyggeskant.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3212,276 +3225,6 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>129999025</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57826</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Sluten/Gåxmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>465248</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6988949</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>129999023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57826</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sluten/Gåxmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>465246</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6988958</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gränssnitslad gran vid en hyggeskant.</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53305-2025 artfynd.xlsx
+++ b/artfynd/A 53305-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999050</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,6 +940,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1065,6 +1080,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1200,6 +1220,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999016</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1335,6 +1360,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1470,6 +1500,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999018</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1605,6 +1640,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1740,6 +1780,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999020</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1875,6 +1920,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2010,6 +2060,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999022</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2145,6 +2200,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999023</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2280,6 +2340,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999024</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2415,6 +2480,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2550,6 +2620,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999026</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2685,6 +2760,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999027</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2820,6 +2900,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999028</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2955,6 +3040,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999029</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3090,6 +3180,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999030</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3225,8 +3320,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129999031</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>